--- a/Function 8/evals.xlsx
+++ b/Function 8/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8229775D-AB5A-409D-83DD-F95271267868}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCCC626-A32C-43E6-98A9-0AABD5C2C33D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Function 8/evals.xlsx
+++ b/Function 8/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCCC626-A32C-43E6-98A9-0AABD5C2C33D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5D061A-4B2E-4B3A-9D52-AC848FEB7A15}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -598,22 +598,50 @@
         <v>0.61394254577440599</v>
       </c>
       <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
+      <c r="T6" s="2">
+        <v>9.8736299406215995</v>
+      </c>
       <c r="U6" s="2"/>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
+      <c r="B7" s="2">
+        <v>5</v>
+      </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="D7" s="2">
+        <v>0.18795969055915701</v>
+      </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="F7" s="2">
+        <v>0.18456120072521301</v>
+      </c>
       <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="H7" s="2">
+        <v>0.20668674319817901</v>
+      </c>
       <c r="I7" s="2"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+      <c r="J7" s="2">
+        <v>0.100105034502231</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2">
+        <v>0.67256431586065202</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2">
+        <v>0.34239458242113802</v>
+      </c>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2">
+        <v>0.245141184722177</v>
+      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2">
+        <v>0.54343843523968005</v>
+      </c>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B8" s="2"/>
@@ -714,19 +742,67 @@
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="82">
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="L5:M5"/>
+  <mergeCells count="88">
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="L4:M4"/>
@@ -743,60 +819,18 @@
     <mergeCell ref="R3:S3"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="L6:M6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 8/evals.xlsx
+++ b/Function 8/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5D061A-4B2E-4B3A-9D52-AC848FEB7A15}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439F02B5-B176-4A03-A62A-296666B5FE9B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -604,10 +604,10 @@
       <c r="U6" s="2"/>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>5</v>
       </c>
-      <c r="C7" s="2"/>
+      <c r="C7" s="3"/>
       <c r="D7" s="2">
         <v>0.18795969055915701</v>
       </c>
@@ -640,36 +640,74 @@
         <v>0.54343843523968005</v>
       </c>
       <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
+      <c r="T7" s="2">
+        <v>9.9258447663276002</v>
+      </c>
       <c r="U7" s="2"/>
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="B8" s="3">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="F8" s="2">
+        <v>6.3831482205849693E-2</v>
+      </c>
       <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="H8" s="2">
+        <v>0.24617402386812101</v>
+      </c>
       <c r="I8" s="2"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+      <c r="J8" s="2">
+        <v>8.1467315280070507E-2</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2">
+        <v>0.84387737150570197</v>
+      </c>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2">
+        <v>0.72912884739503903</v>
+      </c>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2">
+        <v>0.21263725149750201</v>
+      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2">
+        <v>0.54946856351659001</v>
+      </c>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="B9" s="3">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B10" s="2"/>
@@ -742,13 +780,85 @@
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="88">
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="R7:S7"/>
+  <mergeCells count="100">
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
     <mergeCell ref="F11:G11"/>
@@ -765,72 +875,12 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="R7:S7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 8/evals.xlsx
+++ b/Function 8/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439F02B5-B176-4A03-A62A-296666B5FE9B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A105FB-0AD6-49CB-909B-898F377BB51B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -781,30 +781,66 @@
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="L4:M4"/>
@@ -821,66 +857,30 @@
     <mergeCell ref="R3:S3"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 8/evals.xlsx
+++ b/Function 8/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A105FB-0AD6-49CB-909B-898F377BB51B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105CF02E-B4A2-4F25-A360-3B903C01454C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -682,7 +682,9 @@
         <v>0.54946856351659001</v>
       </c>
       <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
+      <c r="T8" s="2">
+        <v>9.8733515165823995</v>
+      </c>
       <c r="U8" s="2"/>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.25">
@@ -690,21 +692,37 @@
         <v>7</v>
       </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="2"/>
+      <c r="D9" s="2">
+        <v>0.14432931989706399</v>
+      </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="F9" s="2">
+        <v>2.3761585627635199E-2</v>
+      </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="H9" s="2">
+        <v>0.26437242580395298</v>
+      </c>
       <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="J9" s="2">
+        <v>0.31843212200239901</v>
+      </c>
       <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="L9" s="2">
+        <v>0.73393484178132695</v>
+      </c>
       <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
+      <c r="N9" s="2">
+        <v>0.47730508965455098</v>
+      </c>
       <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
+      <c r="P9" s="2">
+        <v>1.15766060229903E-2</v>
+      </c>
       <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
+      <c r="R9" s="2">
+        <v>0.509663675452658</v>
+      </c>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
@@ -781,12 +799,84 @@
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
     <mergeCell ref="F11:G11"/>
@@ -803,84 +893,12 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="R7:S7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 8/evals.xlsx
+++ b/Function 8/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105CF02E-B4A2-4F25-A360-3B903C01454C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158341BE-FCBE-430F-8604-B59480117F26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -391,9 +391,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:U14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
       </c>
       <c r="U2" s="2"/>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -477,7 +477,7 @@
       </c>
       <c r="U3" s="2"/>
     </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B4" s="3">
         <v>2</v>
       </c>
@@ -519,7 +519,7 @@
       </c>
       <c r="U4" s="2"/>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
         <v>3</v>
       </c>
@@ -561,7 +561,7 @@
       </c>
       <c r="U5" s="2"/>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
         <v>4</v>
       </c>
@@ -603,7 +603,7 @@
       </c>
       <c r="U6" s="2"/>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
         <v>5</v>
       </c>
@@ -645,7 +645,7 @@
       </c>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
         <v>6</v>
       </c>
@@ -687,7 +687,7 @@
       </c>
       <c r="U8" s="2"/>
     </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <v>7</v>
       </c>
@@ -724,24 +724,52 @@
         <v>0.509663675452658</v>
       </c>
       <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
+      <c r="T9" s="2">
+        <v>9.8230771368129002</v>
+      </c>
       <c r="U9" s="2"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B10" s="3">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="F10" s="2">
+        <v>0.29773137060058802</v>
+      </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2">
+        <v>0.172213071124865</v>
+      </c>
       <c r="I10" s="2"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-    </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="J10" s="2">
+        <v>8.3310765359464994E-2</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2">
+        <v>0.58638862513630896</v>
+      </c>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2">
+        <v>0.56962202601426204</v>
+      </c>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2">
+        <v>0.14459741486230299</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2">
+        <v>0.59029094085021605</v>
+      </c>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+    </row>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -755,7 +783,7 @@
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -769,7 +797,7 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -783,7 +811,7 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -798,31 +826,73 @@
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="100">
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="L5:M5"/>
+  <mergeCells count="106">
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="L4:M4"/>
@@ -839,66 +909,30 @@
     <mergeCell ref="R3:S3"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 8/evals.xlsx
+++ b/Function 8/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158341BE-FCBE-430F-8604-B59480117F26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{192CD2FF-4E94-468D-BF81-E03FBBD9D768}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -391,9 +391,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:U14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
       </c>
       <c r="U2" s="2"/>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -477,7 +477,7 @@
       </c>
       <c r="U3" s="2"/>
     </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
         <v>2</v>
       </c>
@@ -519,7 +519,7 @@
       </c>
       <c r="U4" s="2"/>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>3</v>
       </c>
@@ -561,7 +561,7 @@
       </c>
       <c r="U5" s="2"/>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>4</v>
       </c>
@@ -603,7 +603,7 @@
       </c>
       <c r="U6" s="2"/>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>5</v>
       </c>
@@ -645,7 +645,7 @@
       </c>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>6</v>
       </c>
@@ -687,7 +687,7 @@
       </c>
       <c r="U8" s="2"/>
     </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <v>7</v>
       </c>
@@ -729,7 +729,7 @@
       </c>
       <c r="U9" s="2"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>8</v>
       </c>
@@ -766,38 +766,76 @@
         <v>0.59029094085021605</v>
       </c>
       <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
+      <c r="T10" s="2">
+        <v>9.9145718529803997</v>
+      </c>
       <c r="U10" s="2"/>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B11" s="3">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="F11" s="2">
+        <v>1.7909985921327601E-2</v>
+      </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="H11" s="2">
+        <v>0.13211785894493899</v>
+      </c>
       <c r="I11" s="2"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-    </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="J11" s="2">
+        <v>0.15435240167418701</v>
+      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2">
+        <v>0.65531795284019301</v>
+      </c>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2">
+        <v>0.47223940547386001</v>
+      </c>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2">
+        <v>0.25631326374049901</v>
+      </c>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2">
+        <v>0.58338831639157296</v>
+      </c>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+    </row>
+    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B12" s="3">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-    </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+    </row>
+    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -811,7 +849,7 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -826,35 +864,65 @@
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="106">
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
+  <mergeCells count="118">
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="H14:I14"/>
     <mergeCell ref="F13:G13"/>
@@ -879,36 +947,22 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="T5:U5"/>
     <mergeCell ref="R5:S5"/>
@@ -917,22 +971,18 @@
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="T6:U6"/>
     <mergeCell ref="J6:K6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="R7:S7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 8/evals.xlsx
+++ b/Function 8/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{192CD2FF-4E94-468D-BF81-E03FBBD9D768}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A60579-72C5-4A50-BEA6-5B15EEAF3725}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -391,9 +391,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:U14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
       </c>
       <c r="U2" s="2"/>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -477,7 +477,7 @@
       </c>
       <c r="U3" s="2"/>
     </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B4" s="3">
         <v>2</v>
       </c>
@@ -519,7 +519,7 @@
       </c>
       <c r="U4" s="2"/>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
         <v>3</v>
       </c>
@@ -561,7 +561,7 @@
       </c>
       <c r="U5" s="2"/>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
         <v>4</v>
       </c>
@@ -603,7 +603,7 @@
       </c>
       <c r="U6" s="2"/>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
         <v>5</v>
       </c>
@@ -645,7 +645,7 @@
       </c>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
         <v>6</v>
       </c>
@@ -687,7 +687,7 @@
       </c>
       <c r="U8" s="2"/>
     </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <v>7</v>
       </c>
@@ -729,7 +729,7 @@
       </c>
       <c r="U9" s="2"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>8</v>
       </c>
@@ -771,7 +771,7 @@
       </c>
       <c r="U10" s="2"/>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <v>9</v>
       </c>
@@ -808,34 +808,52 @@
         <v>0.58338831639157296</v>
       </c>
       <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
+      <c r="T11" s="2">
+        <v>9.9449128167485998</v>
+      </c>
       <c r="U11" s="2"/>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <v>10</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="2"/>
+      <c r="D12" s="2">
+        <v>8.2998587192784704E-2</v>
+      </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="F12" s="2">
+        <v>0.20063381415845599</v>
+      </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="H12" s="2">
+        <v>0.157860258230031</v>
+      </c>
       <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+      <c r="J12" s="2">
+        <v>0.204604341175465</v>
+      </c>
       <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="L12" s="2">
+        <v>0.76075961309169404</v>
+      </c>
       <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+      <c r="N12" s="2">
+        <v>0.52639522251767201</v>
+      </c>
       <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
+      <c r="P12" s="2">
+        <v>0.24884093262433901</v>
+      </c>
       <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
+      <c r="R12" s="2">
+        <v>0.47472090220806801</v>
+      </c>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -849,7 +867,7 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -865,65 +883,26 @@
     </row>
   </sheetData>
   <mergeCells count="118">
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="R7:S7"/>
     <mergeCell ref="H14:I14"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
@@ -947,9 +926,17 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D7:E7"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="T4:U4"/>
     <mergeCell ref="F11:G11"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H13:I13"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F10:G10"/>
@@ -963,26 +950,57 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R12:S12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 8/evals.xlsx
+++ b/Function 8/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A60579-72C5-4A50-BEA6-5B15EEAF3725}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7826482-1EB8-4D05-B23A-34A2841F0830}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -391,9 +391,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:U14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
       </c>
       <c r="U2" s="2"/>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -477,7 +477,7 @@
       </c>
       <c r="U3" s="2"/>
     </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
         <v>2</v>
       </c>
@@ -519,7 +519,7 @@
       </c>
       <c r="U4" s="2"/>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>3</v>
       </c>
@@ -561,7 +561,7 @@
       </c>
       <c r="U5" s="2"/>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>4</v>
       </c>
@@ -603,7 +603,7 @@
       </c>
       <c r="U6" s="2"/>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>5</v>
       </c>
@@ -645,7 +645,7 @@
       </c>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>6</v>
       </c>
@@ -687,7 +687,7 @@
       </c>
       <c r="U8" s="2"/>
     </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <v>7</v>
       </c>
@@ -729,7 +729,7 @@
       </c>
       <c r="U9" s="2"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>8</v>
       </c>
@@ -771,7 +771,7 @@
       </c>
       <c r="U10" s="2"/>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <v>9</v>
       </c>
@@ -813,7 +813,7 @@
       </c>
       <c r="U11" s="2"/>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>10</v>
       </c>
@@ -850,24 +850,52 @@
         <v>0.47472090220806801</v>
       </c>
       <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
+      <c r="T12" s="2">
+        <v>9.9837410402549001</v>
+      </c>
       <c r="U12" s="2"/>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B13" s="3">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="2">
+        <v>9.7421073763749602E-2</v>
+      </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="F13" s="2">
+        <v>0.168950759977994</v>
+      </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="H13" s="2">
+        <v>0.165475939063644</v>
+      </c>
       <c r="I13" s="2"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-    </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="J13" s="2">
+        <v>0.16653082408664099</v>
+      </c>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2">
+        <v>0.74975539374142797</v>
+      </c>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2">
+        <v>0.543439470202284</v>
+      </c>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2">
+        <v>0.22742261732549901</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2">
+        <v>0.62769591306210004</v>
+      </c>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -882,27 +910,83 @@
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="118">
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="R7:S7"/>
+  <mergeCells count="124">
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
     <mergeCell ref="H14:I14"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
@@ -927,80 +1011,30 @@
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="F11:G11"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="R7:S7"/>
     <mergeCell ref="N6:O6"/>
     <mergeCell ref="P6:Q6"/>
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="L6:M6"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R12:S12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 8/evals.xlsx
+++ b/Function 8/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7826482-1EB8-4D05-B23A-34A2841F0830}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C76F6B-B8A9-4A20-8682-981812C99C1E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Function 8/evals.xlsx
+++ b/Function 8/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C76F6B-B8A9-4A20-8682-981812C99C1E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE4521C-BF6B-4524-94D6-558D274D6C72}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,9 +98,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -390,603 +389,617 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:U14"/>
+  <dimension ref="B2:U15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="3" t="s">
+      <c r="M2" s="1"/>
+      <c r="N2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="2"/>
-      <c r="P2" s="3" t="s">
+      <c r="O2" s="1"/>
+      <c r="P2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="3" t="s">
+      <c r="Q2" s="1"/>
+      <c r="R2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="2"/>
-      <c r="T2" s="3" t="s">
+      <c r="S2" s="1"/>
+      <c r="T2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="U2" s="2"/>
+      <c r="U2" s="1"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2">
+      <c r="C3" s="2"/>
+      <c r="D3" s="1">
         <v>6.4095426983198298E-3</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="4">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="3">
         <v>9.0589804713272798E-2</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="2">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2">
+      <c r="I3" s="3"/>
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1">
         <v>1</v>
       </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2">
+      <c r="M3" s="1"/>
+      <c r="N3" s="1">
         <v>0.32124777844672298</v>
       </c>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2">
+      <c r="O3" s="1"/>
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1">
         <v>0.35955894285079598</v>
       </c>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2">
+      <c r="S3" s="1"/>
+      <c r="T3" s="1">
         <v>9.7950885401858994</v>
       </c>
-      <c r="U3" s="2"/>
+      <c r="U3" s="1"/>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2">
+      <c r="C4" s="2"/>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1">
         <v>8.8234243210729799E-2</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2">
+      <c r="G4" s="1"/>
+      <c r="H4" s="1">
         <v>0.34090356305633002</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2">
+      <c r="I4" s="1"/>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1">
         <v>0.66597225851339403</v>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2">
+      <c r="M4" s="1"/>
+      <c r="N4" s="1">
         <v>0.45616825190421001</v>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2">
+      <c r="O4" s="1"/>
+      <c r="P4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1">
         <v>1</v>
       </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2">
+      <c r="S4" s="1"/>
+      <c r="T4" s="1">
         <v>9.7133379421200008</v>
       </c>
-      <c r="U4" s="2"/>
+      <c r="U4" s="1"/>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>3</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="2">
+      <c r="C5" s="2"/>
+      <c r="D5" s="1">
         <v>0.14099591177488899</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1">
         <v>2.2376330111608202E-2</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2">
+      <c r="G5" s="1"/>
+      <c r="H5" s="1">
         <v>0.23889345964112199</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2">
+      <c r="I5" s="1"/>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1">
         <v>0.40609780554885999</v>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2">
+      <c r="M5" s="1"/>
+      <c r="N5" s="1">
         <v>0.63452512927791704</v>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2">
+      <c r="O5" s="1"/>
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1">
         <v>0.26517115335536301</v>
       </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2">
+      <c r="S5" s="1"/>
+      <c r="T5" s="1">
         <v>9.7353902998939006</v>
       </c>
-      <c r="U5" s="2"/>
+      <c r="U5" s="1"/>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>4</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2">
+      <c r="C6" s="2"/>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1">
         <v>0.21120330249472</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2">
+      <c r="G6" s="1"/>
+      <c r="H6" s="1">
         <v>9.9415741070405406E-2</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2">
+      <c r="I6" s="1"/>
+      <c r="J6" s="1">
         <v>0.43420921226718001</v>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2">
+      <c r="K6" s="1"/>
+      <c r="L6" s="1">
         <v>0.75873457120409704</v>
       </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2">
+      <c r="M6" s="1"/>
+      <c r="N6" s="1">
         <v>0.61573518728995102</v>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2">
+      <c r="O6" s="1"/>
+      <c r="P6" s="1">
         <v>0.15112345051723</v>
       </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2">
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1">
         <v>0.61394254577440599</v>
       </c>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2">
+      <c r="S6" s="1"/>
+      <c r="T6" s="1">
         <v>9.8736299406215995</v>
       </c>
-      <c r="U6" s="2"/>
+      <c r="U6" s="1"/>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>5</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2">
+      <c r="C7" s="2"/>
+      <c r="D7" s="1">
         <v>0.18795969055915701</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2">
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
         <v>0.18456120072521301</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2">
+      <c r="G7" s="1"/>
+      <c r="H7" s="1">
         <v>0.20668674319817901</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2">
+      <c r="I7" s="1"/>
+      <c r="J7" s="1">
         <v>0.100105034502231</v>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2">
+      <c r="K7" s="1"/>
+      <c r="L7" s="1">
         <v>0.67256431586065202</v>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2">
+      <c r="M7" s="1"/>
+      <c r="N7" s="1">
         <v>0.34239458242113802</v>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2">
+      <c r="O7" s="1"/>
+      <c r="P7" s="1">
         <v>0.245141184722177</v>
       </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2">
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1">
         <v>0.54343843523968005</v>
       </c>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2">
+      <c r="S7" s="1"/>
+      <c r="T7" s="1">
         <v>9.9258447663276002</v>
       </c>
-      <c r="U7" s="2"/>
+      <c r="U7" s="1"/>
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>6</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2">
+      <c r="C8" s="2"/>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
         <v>6.3831482205849693E-2</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2">
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
         <v>0.24617402386812101</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2">
+      <c r="I8" s="1"/>
+      <c r="J8" s="1">
         <v>8.1467315280070507E-2</v>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2">
+      <c r="K8" s="1"/>
+      <c r="L8" s="1">
         <v>0.84387737150570197</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2">
+      <c r="M8" s="1"/>
+      <c r="N8" s="1">
         <v>0.72912884739503903</v>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2">
+      <c r="O8" s="1"/>
+      <c r="P8" s="1">
         <v>0.21263725149750201</v>
       </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2">
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1">
         <v>0.54946856351659001</v>
       </c>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2">
+      <c r="S8" s="1"/>
+      <c r="T8" s="1">
         <v>9.8733515165823995</v>
       </c>
-      <c r="U8" s="2"/>
+      <c r="U8" s="1"/>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>7</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2">
+      <c r="C9" s="2"/>
+      <c r="D9" s="1">
         <v>0.14432931989706399</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2">
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
         <v>2.3761585627635199E-2</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2">
+      <c r="G9" s="1"/>
+      <c r="H9" s="1">
         <v>0.26437242580395298</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2">
+      <c r="I9" s="1"/>
+      <c r="J9" s="1">
         <v>0.31843212200239901</v>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2">
+      <c r="K9" s="1"/>
+      <c r="L9" s="1">
         <v>0.73393484178132695</v>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2">
+      <c r="M9" s="1"/>
+      <c r="N9" s="1">
         <v>0.47730508965455098</v>
       </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2">
+      <c r="O9" s="1"/>
+      <c r="P9" s="1">
         <v>1.15766060229903E-2</v>
       </c>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2">
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1">
         <v>0.509663675452658</v>
       </c>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2">
+      <c r="S9" s="1"/>
+      <c r="T9" s="1">
         <v>9.8230771368129002</v>
       </c>
-      <c r="U9" s="2"/>
+      <c r="U9" s="1"/>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>8</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2">
+      <c r="C10" s="2"/>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
         <v>0.29773137060058802</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2">
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
         <v>0.172213071124865</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2">
+      <c r="I10" s="1"/>
+      <c r="J10" s="1">
         <v>8.3310765359464994E-2</v>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2">
+      <c r="K10" s="1"/>
+      <c r="L10" s="1">
         <v>0.58638862513630896</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2">
+      <c r="M10" s="1"/>
+      <c r="N10" s="1">
         <v>0.56962202601426204</v>
       </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2">
+      <c r="O10" s="1"/>
+      <c r="P10" s="1">
         <v>0.14459741486230299</v>
       </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2">
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1">
         <v>0.59029094085021605</v>
       </c>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2">
+      <c r="S10" s="1"/>
+      <c r="T10" s="1">
         <v>9.9145718529803997</v>
       </c>
-      <c r="U10" s="2"/>
+      <c r="U10" s="1"/>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>9</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2">
+      <c r="C11" s="2"/>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
         <v>1.7909985921327601E-2</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2">
+      <c r="G11" s="1"/>
+      <c r="H11" s="1">
         <v>0.13211785894493899</v>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2">
+      <c r="I11" s="1"/>
+      <c r="J11" s="1">
         <v>0.15435240167418701</v>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2">
+      <c r="K11" s="1"/>
+      <c r="L11" s="1">
         <v>0.65531795284019301</v>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2">
+      <c r="M11" s="1"/>
+      <c r="N11" s="1">
         <v>0.47223940547386001</v>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2">
+      <c r="O11" s="1"/>
+      <c r="P11" s="1">
         <v>0.25631326374049901</v>
       </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2">
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1">
         <v>0.58338831639157296</v>
       </c>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2">
+      <c r="S11" s="1"/>
+      <c r="T11" s="1">
         <v>9.9449128167485998</v>
       </c>
-      <c r="U11" s="2"/>
+      <c r="U11" s="1"/>
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <v>10</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="2">
+      <c r="C12" s="2"/>
+      <c r="D12" s="1">
         <v>8.2998587192784704E-2</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
         <v>0.20063381415845599</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2">
+      <c r="G12" s="1"/>
+      <c r="H12" s="1">
         <v>0.157860258230031</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2">
+      <c r="I12" s="1"/>
+      <c r="J12" s="1">
         <v>0.204604341175465</v>
       </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2">
+      <c r="K12" s="1"/>
+      <c r="L12" s="1">
         <v>0.76075961309169404</v>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2">
+      <c r="M12" s="1"/>
+      <c r="N12" s="1">
         <v>0.52639522251767201</v>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2">
+      <c r="O12" s="1"/>
+      <c r="P12" s="1">
         <v>0.24884093262433901</v>
       </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2">
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1">
         <v>0.47472090220806801</v>
       </c>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2">
+      <c r="S12" s="1"/>
+      <c r="T12" s="1">
         <v>9.9837410402549001</v>
       </c>
-      <c r="U12" s="2"/>
+      <c r="U12" s="1"/>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <v>11</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="2">
+      <c r="C13" s="2"/>
+      <c r="D13" s="1">
         <v>9.7421073763749602E-2</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
         <v>0.168950759977994</v>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2">
+      <c r="G13" s="1"/>
+      <c r="H13" s="1">
         <v>0.165475939063644</v>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2">
+      <c r="I13" s="1"/>
+      <c r="J13" s="1">
         <v>0.16653082408664099</v>
       </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2">
+      <c r="K13" s="1"/>
+      <c r="L13" s="1">
         <v>0.74975539374142797</v>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2">
+      <c r="M13" s="1"/>
+      <c r="N13" s="1">
         <v>0.543439470202284</v>
       </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2">
+      <c r="O13" s="1"/>
+      <c r="P13" s="1">
         <v>0.22742261732549901</v>
       </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2">
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1">
         <v>0.62769591306210004</v>
       </c>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1">
+        <v>9.9908486679949</v>
+      </c>
+      <c r="U13" s="1"/>
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
+      <c r="B14" s="2">
+        <v>12</v>
+      </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="1"/>
+      <c r="D14" s="1">
+        <v>7.7528147615390994E-2</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1">
+        <v>0.18917413646310699</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1">
+        <v>0.194828639281345</v>
+      </c>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1">
+        <v>0.20981631028766901</v>
+      </c>
       <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="L14" s="1">
+        <v>0.70416517136721901</v>
+      </c>
       <c r="M14" s="1"/>
+      <c r="N14" s="1">
+        <v>0.53505979076548604</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1">
+        <v>0.256154614974758</v>
+      </c>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1">
+        <v>0.59353257544119398</v>
+      </c>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="124">
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
+  <mergeCells count="140">
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="L6:M6"/>
     <mergeCell ref="H14:I14"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
@@ -1011,30 +1024,82 @@
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="F11:G11"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R12:S12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
